--- a/results/throughput_45threads.xlsx
+++ b/results/throughput_45threads.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kone_file/Desktop/6650/SkiTrak-System/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2BF628-C736-F940-BCFD-25B0D8777B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA9822D-48D4-2645-8AFB-CD5A93255CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-32160" yWindow="1220" windowWidth="27640" windowHeight="16260" xr2:uid="{8A3CFBF1-B042-FB48-B010-41EBB56509F6}"/>
   </bookViews>
@@ -1473,6 +1473,7 @@
         <c:axId val="1160220128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="800"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -3267,10 +3268,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB0A3EA3-F45B-4B41-8742-6ECBF9ABC22A}">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3278,23 +3279,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
         <v>639.70000000000005</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="D2">
+        <v>62</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>10</v>
       </c>
       <c r="B3">
         <v>695.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="D3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>20</v>
       </c>
@@ -3302,7 +3312,7 @@
         <v>669.9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>30</v>
       </c>
@@ -3310,7 +3320,7 @@
         <v>556.1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>40</v>
       </c>
@@ -3318,7 +3328,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>50</v>
       </c>
@@ -3326,7 +3336,7 @@
         <v>317.2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>60</v>
       </c>
@@ -3334,7 +3344,7 @@
         <v>354.5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>70</v>
       </c>
@@ -3342,7 +3352,7 @@
         <v>430.9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>80</v>
       </c>
@@ -3350,7 +3360,7 @@
         <v>615.79999999999995</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>90</v>
       </c>
@@ -3358,7 +3368,7 @@
         <v>637.70000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>100</v>
       </c>
@@ -3366,7 +3376,7 @@
         <v>730.5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>110</v>
       </c>
@@ -3374,7 +3384,7 @@
         <v>796.3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>120</v>
       </c>
@@ -3382,7 +3392,7 @@
         <v>747.3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>130</v>
       </c>
@@ -3390,7 +3400,7 @@
         <v>697.7</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>140</v>
       </c>
